--- a/markets/invest_map/dist/20261026_AI投資地圖_資料_v0.5.1.xlsx
+++ b/markets/invest_map/dist/20261026_AI投資地圖_資料_v0.5.1.xlsx
@@ -514,7 +514,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>收支關卡（Andy 2026-10-25 10:48）：先看收支、再看評價。模型期間（2026 起約五年）現金收支合計為負＝入不敷出、有資金缺口，不論估值空間多大，最終分級一律為「收支不足」。口徑：雲端／neocloud／MAG 模板一律用「營運缺口＋股東回饋（股利、回購）」；記憶體、模型商用自由現金流；只有損益的半導體模型以「各情境淨利皆為正」判定（現金流本專案未建立）。</t>
+          <t>收支關卡（Andy 2026-10-25 10:48）：先看收支、再看評價。模型期間（2026 起約五年）現金收支合計為負＝入不敷出、有資金缺口，評價為買進以上（或未估值）者，最終分級改為「收支不足」；評價為中立、放空、強力放空者維持原評價，入不敷出只加重放空理由（Andy 2026-10-26 修訂）。口徑：雲端／neocloud／MAG 模板一律用「營運缺口＋股東回饋（股利、回購）」；記憶體、模型商用自由現金流；只有損益的半導體模型以「各情境淨利皆為正」判定（現金流本專案未建立）。</t>
         </is>
       </c>
     </row>
@@ -7910,7 +7910,7 @@
         <v/>
       </c>
       <c r="AI2">
-        <f>IF(S2="未上市","未上市",IF(AH2="不通過","收支不足",S2))</f>
+        <f>IF(S2="未上市","未上市",IF(AND(AH2="不通過",OR(S2="強力買進",S2="買進",S2="未估值")),"收支不足",S2))</f>
         <v/>
       </c>
       <c r="AJ2">
@@ -8045,7 +8045,7 @@
         <v/>
       </c>
       <c r="AI3">
-        <f>IF(S3="未上市","未上市",IF(AH3="不通過","收支不足",S3))</f>
+        <f>IF(S3="未上市","未上市",IF(AND(AH3="不通過",OR(S3="強力買進",S3="買進",S3="未估值")),"收支不足",S3))</f>
         <v/>
       </c>
       <c r="AJ3">
@@ -8175,7 +8175,7 @@
         <v/>
       </c>
       <c r="AI4">
-        <f>IF(S4="未上市","未上市",IF(AH4="不通過","收支不足",S4))</f>
+        <f>IF(S4="未上市","未上市",IF(AND(AH4="不通過",OR(S4="強力買進",S4="買進",S4="未估值")),"收支不足",S4))</f>
         <v/>
       </c>
       <c r="AJ4">
@@ -8305,7 +8305,7 @@
         <v/>
       </c>
       <c r="AI5">
-        <f>IF(S5="未上市","未上市",IF(AH5="不通過","收支不足",S5))</f>
+        <f>IF(S5="未上市","未上市",IF(AND(AH5="不通過",OR(S5="強力買進",S5="買進",S5="未估值")),"收支不足",S5))</f>
         <v/>
       </c>
       <c r="AJ5">
@@ -8435,7 +8435,7 @@
         <v/>
       </c>
       <c r="AI6">
-        <f>IF(S6="未上市","未上市",IF(AH6="不通過","收支不足",S6))</f>
+        <f>IF(S6="未上市","未上市",IF(AND(AH6="不通過",OR(S6="強力買進",S6="買進",S6="未估值")),"收支不足",S6))</f>
         <v/>
       </c>
       <c r="AJ6">
@@ -8565,7 +8565,7 @@
         <v/>
       </c>
       <c r="AI7">
-        <f>IF(S7="未上市","未上市",IF(AH7="不通過","收支不足",S7))</f>
+        <f>IF(S7="未上市","未上市",IF(AND(AH7="不通過",OR(S7="強力買進",S7="買進",S7="未估值")),"收支不足",S7))</f>
         <v/>
       </c>
       <c r="AJ7">
@@ -8700,7 +8700,7 @@
         <v/>
       </c>
       <c r="AI8">
-        <f>IF(S8="未上市","未上市",IF(AH8="不通過","收支不足",S8))</f>
+        <f>IF(S8="未上市","未上市",IF(AND(AH8="不通過",OR(S8="強力買進",S8="買進",S8="未估值")),"收支不足",S8))</f>
         <v/>
       </c>
       <c r="AJ8">
@@ -8835,7 +8835,7 @@
         <v/>
       </c>
       <c r="AI9">
-        <f>IF(S9="未上市","未上市",IF(AH9="不通過","收支不足",S9))</f>
+        <f>IF(S9="未上市","未上市",IF(AND(AH9="不通過",OR(S9="強力買進",S9="買進",S9="未估值")),"收支不足",S9))</f>
         <v/>
       </c>
       <c r="AJ9">
@@ -8970,7 +8970,7 @@
         <v/>
       </c>
       <c r="AI10">
-        <f>IF(S10="未上市","未上市",IF(AH10="不通過","收支不足",S10))</f>
+        <f>IF(S10="未上市","未上市",IF(AND(AH10="不通過",OR(S10="強力買進",S10="買進",S10="未估值")),"收支不足",S10))</f>
         <v/>
       </c>
       <c r="AJ10">
@@ -9105,7 +9105,7 @@
         <v/>
       </c>
       <c r="AI11">
-        <f>IF(S11="未上市","未上市",IF(AH11="不通過","收支不足",S11))</f>
+        <f>IF(S11="未上市","未上市",IF(AND(AH11="不通過",OR(S11="強力買進",S11="買進",S11="未估值")),"收支不足",S11))</f>
         <v/>
       </c>
       <c r="AJ11">
@@ -9240,7 +9240,7 @@
         <v/>
       </c>
       <c r="AI12">
-        <f>IF(S12="未上市","未上市",IF(AH12="不通過","收支不足",S12))</f>
+        <f>IF(S12="未上市","未上市",IF(AND(AH12="不通過",OR(S12="強力買進",S12="買進",S12="未估值")),"收支不足",S12))</f>
         <v/>
       </c>
       <c r="AJ12">
@@ -9370,7 +9370,7 @@
         <v/>
       </c>
       <c r="AI13">
-        <f>IF(S13="未上市","未上市",IF(AH13="不通過","收支不足",S13))</f>
+        <f>IF(S13="未上市","未上市",IF(AND(AH13="不通過",OR(S13="強力買進",S13="買進",S13="未估值")),"收支不足",S13))</f>
         <v/>
       </c>
       <c r="AJ13">
@@ -9500,7 +9500,7 @@
         <v/>
       </c>
       <c r="AI14">
-        <f>IF(S14="未上市","未上市",IF(AH14="不通過","收支不足",S14))</f>
+        <f>IF(S14="未上市","未上市",IF(AND(AH14="不通過",OR(S14="強力買進",S14="買進",S14="未估值")),"收支不足",S14))</f>
         <v/>
       </c>
       <c r="AJ14">
@@ -9630,7 +9630,7 @@
         <v/>
       </c>
       <c r="AI15">
-        <f>IF(S15="未上市","未上市",IF(AH15="不通過","收支不足",S15))</f>
+        <f>IF(S15="未上市","未上市",IF(AND(AH15="不通過",OR(S15="強力買進",S15="買進",S15="未估值")),"收支不足",S15))</f>
         <v/>
       </c>
       <c r="AJ15">
@@ -9760,7 +9760,7 @@
         <v/>
       </c>
       <c r="AI16">
-        <f>IF(S16="未上市","未上市",IF(AH16="不通過","收支不足",S16))</f>
+        <f>IF(S16="未上市","未上市",IF(AND(AH16="不通過",OR(S16="強力買進",S16="買進",S16="未估值")),"收支不足",S16))</f>
         <v/>
       </c>
       <c r="AJ16">
@@ -9890,7 +9890,7 @@
         <v/>
       </c>
       <c r="AI17">
-        <f>IF(S17="未上市","未上市",IF(AH17="不通過","收支不足",S17))</f>
+        <f>IF(S17="未上市","未上市",IF(AND(AH17="不通過",OR(S17="強力買進",S17="買進",S17="未估值")),"收支不足",S17))</f>
         <v/>
       </c>
       <c r="AJ17">
@@ -10020,7 +10020,7 @@
         <v/>
       </c>
       <c r="AI18">
-        <f>IF(S18="未上市","未上市",IF(AH18="不通過","收支不足",S18))</f>
+        <f>IF(S18="未上市","未上市",IF(AND(AH18="不通過",OR(S18="強力買進",S18="買進",S18="未估值")),"收支不足",S18))</f>
         <v/>
       </c>
       <c r="AJ18">
@@ -10150,7 +10150,7 @@
         <v/>
       </c>
       <c r="AI19">
-        <f>IF(S19="未上市","未上市",IF(AH19="不通過","收支不足",S19))</f>
+        <f>IF(S19="未上市","未上市",IF(AND(AH19="不通過",OR(S19="強力買進",S19="買進",S19="未估值")),"收支不足",S19))</f>
         <v/>
       </c>
       <c r="AJ19">
@@ -10280,7 +10280,7 @@
         <v/>
       </c>
       <c r="AI20">
-        <f>IF(S20="未上市","未上市",IF(AH20="不通過","收支不足",S20))</f>
+        <f>IF(S20="未上市","未上市",IF(AND(AH20="不通過",OR(S20="強力買進",S20="買進",S20="未估值")),"收支不足",S20))</f>
         <v/>
       </c>
       <c r="AJ20">
@@ -10410,7 +10410,7 @@
         <v/>
       </c>
       <c r="AI21">
-        <f>IF(S21="未上市","未上市",IF(AH21="不通過","收支不足",S21))</f>
+        <f>IF(S21="未上市","未上市",IF(AND(AH21="不通過",OR(S21="強力買進",S21="買進",S21="未估值")),"收支不足",S21))</f>
         <v/>
       </c>
       <c r="AJ21">
@@ -10533,7 +10533,7 @@
         <v/>
       </c>
       <c r="AI22">
-        <f>IF(S22="未上市","未上市",IF(AH22="不通過","收支不足",S22))</f>
+        <f>IF(S22="未上市","未上市",IF(AND(AH22="不通過",OR(S22="強力買進",S22="買進",S22="未估值")),"收支不足",S22))</f>
         <v/>
       </c>
       <c r="AJ22">
@@ -10624,7 +10624,7 @@
         <v/>
       </c>
       <c r="AI23">
-        <f>IF(S23="未上市","未上市",IF(AH23="不通過","收支不足",S23))</f>
+        <f>IF(S23="未上市","未上市",IF(AND(AH23="不通過",OR(S23="強力買進",S23="買進",S23="未估值")),"收支不足",S23))</f>
         <v/>
       </c>
     </row>
@@ -10706,7 +10706,7 @@
         <v/>
       </c>
       <c r="AI24">
-        <f>IF(S24="未上市","未上市",IF(AH24="不通過","收支不足",S24))</f>
+        <f>IF(S24="未上市","未上市",IF(AND(AH24="不通過",OR(S24="強力買進",S24="買進",S24="未估值")),"收支不足",S24))</f>
         <v/>
       </c>
     </row>
@@ -10788,7 +10788,7 @@
         <v/>
       </c>
       <c r="AI25">
-        <f>IF(S25="未上市","未上市",IF(AH25="不通過","收支不足",S25))</f>
+        <f>IF(S25="未上市","未上市",IF(AND(AH25="不通過",OR(S25="強力買進",S25="買進",S25="未估值")),"收支不足",S25))</f>
         <v/>
       </c>
     </row>
@@ -10914,7 +10914,7 @@
         <v/>
       </c>
       <c r="AI26">
-        <f>IF(S26="未上市","未上市",IF(AH26="不通過","收支不足",S26))</f>
+        <f>IF(S26="未上市","未上市",IF(AND(AH26="不通過",OR(S26="強力買進",S26="買進",S26="未估值")),"收支不足",S26))</f>
         <v/>
       </c>
       <c r="AJ26">
@@ -11040,7 +11040,7 @@
         <v/>
       </c>
       <c r="AI27">
-        <f>IF(S27="未上市","未上市",IF(AH27="不通過","收支不足",S27))</f>
+        <f>IF(S27="未上市","未上市",IF(AND(AH27="不通過",OR(S27="強力買進",S27="買進",S27="未估值")),"收支不足",S27))</f>
         <v/>
       </c>
       <c r="AJ27">
@@ -11175,7 +11175,7 @@
         <v/>
       </c>
       <c r="AI28">
-        <f>IF(S28="未上市","未上市",IF(AH28="不通過","收支不足",S28))</f>
+        <f>IF(S28="未上市","未上市",IF(AND(AH28="不通過",OR(S28="強力買進",S28="買進",S28="未估值")),"收支不足",S28))</f>
         <v/>
       </c>
       <c r="AJ28">
@@ -11301,7 +11301,7 @@
         <v/>
       </c>
       <c r="AI29">
-        <f>IF(S29="未上市","未上市",IF(AH29="不通過","收支不足",S29))</f>
+        <f>IF(S29="未上市","未上市",IF(AND(AH29="不通過",OR(S29="強力買進",S29="買進",S29="未估值")),"收支不足",S29))</f>
         <v/>
       </c>
       <c r="AJ29">
@@ -11427,7 +11427,7 @@
         <v/>
       </c>
       <c r="AI30">
-        <f>IF(S30="未上市","未上市",IF(AH30="不通過","收支不足",S30))</f>
+        <f>IF(S30="未上市","未上市",IF(AND(AH30="不通過",OR(S30="強力買進",S30="買進",S30="未估值")),"收支不足",S30))</f>
         <v/>
       </c>
       <c r="AJ30">
@@ -11563,7 +11563,7 @@
         <v/>
       </c>
       <c r="AI31">
-        <f>IF(S31="未上市","未上市",IF(AH31="不通過","收支不足",S31))</f>
+        <f>IF(S31="未上市","未上市",IF(AND(AH31="不通過",OR(S31="強力買進",S31="買進",S31="未估值")),"收支不足",S31))</f>
         <v/>
       </c>
       <c r="AJ31" s="4" t="inlineStr">
@@ -11700,7 +11700,7 @@
         <v/>
       </c>
       <c r="AI32">
-        <f>IF(S32="未上市","未上市",IF(AH32="不通過","收支不足",S32))</f>
+        <f>IF(S32="未上市","未上市",IF(AND(AH32="不通過",OR(S32="強力買進",S32="買進",S32="未估值")),"收支不足",S32))</f>
         <v/>
       </c>
       <c r="AJ32" s="4" t="inlineStr">
@@ -11836,7 +11836,7 @@
         <v/>
       </c>
       <c r="AI33">
-        <f>IF(S33="未上市","未上市",IF(AH33="不通過","收支不足",S33))</f>
+        <f>IF(S33="未上市","未上市",IF(AND(AH33="不通過",OR(S33="強力買進",S33="買進",S33="未估值")),"收支不足",S33))</f>
         <v/>
       </c>
       <c r="AJ33">
@@ -11971,7 +11971,7 @@
         <v/>
       </c>
       <c r="AI34">
-        <f>IF(S34="未上市","未上市",IF(AH34="不通過","收支不足",S34))</f>
+        <f>IF(S34="未上市","未上市",IF(AND(AH34="不通過",OR(S34="強力買進",S34="買進",S34="未估值")),"收支不足",S34))</f>
         <v/>
       </c>
       <c r="AJ34">
@@ -12106,7 +12106,7 @@
         <v/>
       </c>
       <c r="AI35">
-        <f>IF(S35="未上市","未上市",IF(AH35="不通過","收支不足",S35))</f>
+        <f>IF(S35="未上市","未上市",IF(AND(AH35="不通過",OR(S35="強力買進",S35="買進",S35="未估值")),"收支不足",S35))</f>
         <v/>
       </c>
       <c r="AJ35">
@@ -12241,7 +12241,7 @@
         <v/>
       </c>
       <c r="AI36">
-        <f>IF(S36="未上市","未上市",IF(AH36="不通過","收支不足",S36))</f>
+        <f>IF(S36="未上市","未上市",IF(AND(AH36="不通過",OR(S36="強力買進",S36="買進",S36="未估值")),"收支不足",S36))</f>
         <v/>
       </c>
       <c r="AJ36">
@@ -12376,7 +12376,7 @@
         <v/>
       </c>
       <c r="AI37">
-        <f>IF(S37="未上市","未上市",IF(AH37="不通過","收支不足",S37))</f>
+        <f>IF(S37="未上市","未上市",IF(AND(AH37="不通過",OR(S37="強力買進",S37="買進",S37="未估值")),"收支不足",S37))</f>
         <v/>
       </c>
       <c r="AJ37">
@@ -12511,7 +12511,7 @@
         <v/>
       </c>
       <c r="AI38">
-        <f>IF(S38="未上市","未上市",IF(AH38="不通過","收支不足",S38))</f>
+        <f>IF(S38="未上市","未上市",IF(AND(AH38="不通過",OR(S38="強力買進",S38="買進",S38="未估值")),"收支不足",S38))</f>
         <v/>
       </c>
       <c r="AJ38">
@@ -12646,7 +12646,7 @@
         <v/>
       </c>
       <c r="AI39">
-        <f>IF(S39="未上市","未上市",IF(AH39="不通過","收支不足",S39))</f>
+        <f>IF(S39="未上市","未上市",IF(AND(AH39="不通過",OR(S39="強力買進",S39="買進",S39="未估值")),"收支不足",S39))</f>
         <v/>
       </c>
       <c r="AJ39">
@@ -12772,7 +12772,7 @@
         <v/>
       </c>
       <c r="AI40">
-        <f>IF(S40="未上市","未上市",IF(AH40="不通過","收支不足",S40))</f>
+        <f>IF(S40="未上市","未上市",IF(AND(AH40="不通過",OR(S40="強力買進",S40="買進",S40="未估值")),"收支不足",S40))</f>
         <v/>
       </c>
       <c r="AJ40">
@@ -12898,7 +12898,7 @@
         <v/>
       </c>
       <c r="AI41">
-        <f>IF(S41="未上市","未上市",IF(AH41="不通過","收支不足",S41))</f>
+        <f>IF(S41="未上市","未上市",IF(AND(AH41="不通過",OR(S41="強力買進",S41="買進",S41="未估值")),"收支不足",S41))</f>
         <v/>
       </c>
       <c r="AJ41">
@@ -13033,7 +13033,7 @@
         <v/>
       </c>
       <c r="AI42">
-        <f>IF(S42="未上市","未上市",IF(AH42="不通過","收支不足",S42))</f>
+        <f>IF(S42="未上市","未上市",IF(AND(AH42="不通過",OR(S42="強力買進",S42="買進",S42="未估值")),"收支不足",S42))</f>
         <v/>
       </c>
       <c r="AJ42">
@@ -13159,7 +13159,7 @@
         <v/>
       </c>
       <c r="AI43">
-        <f>IF(S43="未上市","未上市",IF(AH43="不通過","收支不足",S43))</f>
+        <f>IF(S43="未上市","未上市",IF(AND(AH43="不通過",OR(S43="強力買進",S43="買進",S43="未估值")),"收支不足",S43))</f>
         <v/>
       </c>
       <c r="AJ43">
@@ -13285,7 +13285,7 @@
         <v/>
       </c>
       <c r="AI44">
-        <f>IF(S44="未上市","未上市",IF(AH44="不通過","收支不足",S44))</f>
+        <f>IF(S44="未上市","未上市",IF(AND(AH44="不通過",OR(S44="強力買進",S44="買進",S44="未估值")),"收支不足",S44))</f>
         <v/>
       </c>
       <c r="AJ44">
@@ -13411,7 +13411,7 @@
         <v/>
       </c>
       <c r="AI45">
-        <f>IF(S45="未上市","未上市",IF(AH45="不通過","收支不足",S45))</f>
+        <f>IF(S45="未上市","未上市",IF(AND(AH45="不通過",OR(S45="強力買進",S45="買進",S45="未估值")),"收支不足",S45))</f>
         <v/>
       </c>
       <c r="AJ45">
@@ -13537,7 +13537,7 @@
         <v/>
       </c>
       <c r="AI46">
-        <f>IF(S46="未上市","未上市",IF(AH46="不通過","收支不足",S46))</f>
+        <f>IF(S46="未上市","未上市",IF(AND(AH46="不通過",OR(S46="強力買進",S46="買進",S46="未估值")),"收支不足",S46))</f>
         <v/>
       </c>
       <c r="AJ46">
@@ -13672,7 +13672,7 @@
         <v/>
       </c>
       <c r="AI47">
-        <f>IF(S47="未上市","未上市",IF(AH47="不通過","收支不足",S47))</f>
+        <f>IF(S47="未上市","未上市",IF(AND(AH47="不通過",OR(S47="強力買進",S47="買進",S47="未估值")),"收支不足",S47))</f>
         <v/>
       </c>
       <c r="AJ47">
@@ -13807,7 +13807,7 @@
         <v/>
       </c>
       <c r="AI48">
-        <f>IF(S48="未上市","未上市",IF(AH48="不通過","收支不足",S48))</f>
+        <f>IF(S48="未上市","未上市",IF(AND(AH48="不通過",OR(S48="強力買進",S48="買進",S48="未估值")),"收支不足",S48))</f>
         <v/>
       </c>
       <c r="AJ48">
@@ -13942,7 +13942,7 @@
         <v/>
       </c>
       <c r="AI49">
-        <f>IF(S49="未上市","未上市",IF(AH49="不通過","收支不足",S49))</f>
+        <f>IF(S49="未上市","未上市",IF(AND(AH49="不通過",OR(S49="強力買進",S49="買進",S49="未估值")),"收支不足",S49))</f>
         <v/>
       </c>
       <c r="AJ49">
@@ -14077,7 +14077,7 @@
         <v/>
       </c>
       <c r="AI50">
-        <f>IF(S50="未上市","未上市",IF(AH50="不通過","收支不足",S50))</f>
+        <f>IF(S50="未上市","未上市",IF(AND(AH50="不通過",OR(S50="強力買進",S50="買進",S50="未估值")),"收支不足",S50))</f>
         <v/>
       </c>
       <c r="AJ50">
@@ -14212,7 +14212,7 @@
         <v/>
       </c>
       <c r="AI51">
-        <f>IF(S51="未上市","未上市",IF(AH51="不通過","收支不足",S51))</f>
+        <f>IF(S51="未上市","未上市",IF(AND(AH51="不通過",OR(S51="強力買進",S51="買進",S51="未估值")),"收支不足",S51))</f>
         <v/>
       </c>
       <c r="AJ51">
@@ -14347,7 +14347,7 @@
         <v/>
       </c>
       <c r="AI52">
-        <f>IF(S52="未上市","未上市",IF(AH52="不通過","收支不足",S52))</f>
+        <f>IF(S52="未上市","未上市",IF(AND(AH52="不通過",OR(S52="強力買進",S52="買進",S52="未估值")),"收支不足",S52))</f>
         <v/>
       </c>
       <c r="AJ52">
@@ -14482,7 +14482,7 @@
         <v/>
       </c>
       <c r="AI53">
-        <f>IF(S53="未上市","未上市",IF(AH53="不通過","收支不足",S53))</f>
+        <f>IF(S53="未上市","未上市",IF(AND(AH53="不通過",OR(S53="強力買進",S53="買進",S53="未估值")),"收支不足",S53))</f>
         <v/>
       </c>
       <c r="AJ53">
@@ -14617,7 +14617,7 @@
         <v/>
       </c>
       <c r="AI54">
-        <f>IF(S54="未上市","未上市",IF(AH54="不通過","收支不足",S54))</f>
+        <f>IF(S54="未上市","未上市",IF(AND(AH54="不通過",OR(S54="強力買進",S54="買進",S54="未估值")),"收支不足",S54))</f>
         <v/>
       </c>
       <c r="AJ54">
@@ -14752,7 +14752,7 @@
         <v/>
       </c>
       <c r="AI55">
-        <f>IF(S55="未上市","未上市",IF(AH55="不通過","收支不足",S55))</f>
+        <f>IF(S55="未上市","未上市",IF(AND(AH55="不通過",OR(S55="強力買進",S55="買進",S55="未估值")),"收支不足",S55))</f>
         <v/>
       </c>
       <c r="AJ55">
@@ -14887,7 +14887,7 @@
         <v/>
       </c>
       <c r="AI56">
-        <f>IF(S56="未上市","未上市",IF(AH56="不通過","收支不足",S56))</f>
+        <f>IF(S56="未上市","未上市",IF(AND(AH56="不通過",OR(S56="強力買進",S56="買進",S56="未估值")),"收支不足",S56))</f>
         <v/>
       </c>
       <c r="AJ56">
@@ -15013,7 +15013,7 @@
         <v/>
       </c>
       <c r="AI57">
-        <f>IF(S57="未上市","未上市",IF(AH57="不通過","收支不足",S57))</f>
+        <f>IF(S57="未上市","未上市",IF(AND(AH57="不通過",OR(S57="強力買進",S57="買進",S57="未估值")),"收支不足",S57))</f>
         <v/>
       </c>
       <c r="AJ57">
@@ -15139,7 +15139,7 @@
         <v/>
       </c>
       <c r="AI58">
-        <f>IF(S58="未上市","未上市",IF(AH58="不通過","收支不足",S58))</f>
+        <f>IF(S58="未上市","未上市",IF(AND(AH58="不通過",OR(S58="強力買進",S58="買進",S58="未估值")),"收支不足",S58))</f>
         <v/>
       </c>
       <c r="AJ58">
@@ -15266,7 +15266,7 @@
         <v/>
       </c>
       <c r="AI59">
-        <f>IF(S59="未上市","未上市",IF(AH59="不通過","收支不足",S59))</f>
+        <f>IF(S59="未上市","未上市",IF(AND(AH59="不通過",OR(S59="強力買進",S59="買進",S59="未估值")),"收支不足",S59))</f>
         <v/>
       </c>
       <c r="AJ59" s="4" t="inlineStr">
@@ -15393,7 +15393,7 @@
         <v/>
       </c>
       <c r="AI60">
-        <f>IF(S60="未上市","未上市",IF(AH60="不通過","收支不足",S60))</f>
+        <f>IF(S60="未上市","未上市",IF(AND(AH60="不通過",OR(S60="強力買進",S60="買進",S60="未估值")),"收支不足",S60))</f>
         <v/>
       </c>
       <c r="AJ60">
@@ -15528,7 +15528,7 @@
         <v/>
       </c>
       <c r="AI61">
-        <f>IF(S61="未上市","未上市",IF(AH61="不通過","收支不足",S61))</f>
+        <f>IF(S61="未上市","未上市",IF(AND(AH61="不通過",OR(S61="強力買進",S61="買進",S61="未估值")),"收支不足",S61))</f>
         <v/>
       </c>
       <c r="AJ61">
@@ -15654,7 +15654,7 @@
         <v/>
       </c>
       <c r="AI62">
-        <f>IF(S62="未上市","未上市",IF(AH62="不通過","收支不足",S62))</f>
+        <f>IF(S62="未上市","未上市",IF(AND(AH62="不通過",OR(S62="強力買進",S62="買進",S62="未估值")),"收支不足",S62))</f>
         <v/>
       </c>
       <c r="AJ62">
@@ -15780,7 +15780,7 @@
         <v/>
       </c>
       <c r="AI63">
-        <f>IF(S63="未上市","未上市",IF(AH63="不通過","收支不足",S63))</f>
+        <f>IF(S63="未上市","未上市",IF(AND(AH63="不通過",OR(S63="強力買進",S63="買進",S63="未估值")),"收支不足",S63))</f>
         <v/>
       </c>
       <c r="AJ63">
@@ -15907,7 +15907,7 @@
         <v/>
       </c>
       <c r="AI64">
-        <f>IF(S64="未上市","未上市",IF(AH64="不通過","收支不足",S64))</f>
+        <f>IF(S64="未上市","未上市",IF(AND(AH64="不通過",OR(S64="強力買進",S64="買進",S64="未估值")),"收支不足",S64))</f>
         <v/>
       </c>
       <c r="AJ64" s="4" t="inlineStr">
